--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1656C4-B6F0-4682-BFD6-B9D17A960D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E8FCEF5AC0071D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{076EEF79-6D6A-4F10-B184-19D422565F7E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 09-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 14-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E8FCEF5AC0071D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{076EEF79-6D6A-4F10-B184-19D422565F7E}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2EBCEEB5850870D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8546F389-93A9-42A4-8E0E-65D53B3090CA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2EBCEEB5850870D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8546F389-93A9-42A4-8E0E-65D53B3090CA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3249D84C-001E-4272-B945-54B5FEE56BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3249D84C-001E-4272-B945-54B5FEE56BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA790FB-DD1A-4EB8-BDDA-972F6D08FD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 14-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 17-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA790FB-DD1A-4EB8-BDDA-972F6D08FD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF95369-89E8-429C-B9ED-933AC198A61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF95369-89E8-429C-B9ED-933AC198A61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A3E5FB-95BA-4F35-8F93-96A7736644E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 17-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 21-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A3E5FB-95BA-4F35-8F93-96A7736644E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFDC5B4-92C8-45C9-8CB6-47135336048C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 21-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 22-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFDC5B4-92C8-45C9-8CB6-47135336048C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896FB814-3261-45B0-85F0-4A0B4D42A711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896FB814-3261-45B0-85F0-4A0B4D42A711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4185BD3-A39D-4876-91FC-B0ECCACEF36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 22-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 23-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4185BD3-A39D-4876-91FC-B0ECCACEF36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E6766738C4A71D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB1E32B-81DE-4FAD-BF35-705D288241FE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E6766738C4A71D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB1E32B-81DE-4FAD-BF35-705D288241FE}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E70BEF2A61A71D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEE14234-6AB1-48AF-91AF-0963DFAF1803}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 23-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 24-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E70BEF2A61A71D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEE14234-6AB1-48AF-91AF-0963DFAF1803}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E0EAEB08B0271D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EA5F59A-577C-49B5-BA4B-69C39909D751}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E0EAEB08B0271D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EA5F59A-577C-49B5-BA4B-69C39909D751}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2D739B-3484-4A20-B094-1A26F0AE73FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 24-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 28-09-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2D739B-3484-4A20-B094-1A26F0AE73FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E8176F7AEB471D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D46A8715-4426-463A-8EDA-EF2E7F74E00A}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 28-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 02-10-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896FB814-3261-45B0-85F0-4A0B4D42A711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB06FAC-BC15-47AA-92E4-E872FF98F2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 22-09-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 07-10-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E8176F7AEB471D8A5C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D46A8715-4426-463A-8EDA-EF2E7F74E00A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E43B0E-FB5D-4F64-8C54-07AE8B2302D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 02-10-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 07-10-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -482,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -540,7 +540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -666,7 +666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -680,7 +680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -694,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -708,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -736,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -764,7 +764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E43B0E-FB5D-4F64-8C54-07AE8B2302D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2EF9C6B4915E71D8A5DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34A4CA29-99BF-4AFB-9002-F83A85FC856E}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 07-10-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 08-10-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2EF9C6B4915E71D8A5DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34A4CA29-99BF-4AFB-9002-F83A85FC856E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A73DF3-086A-4F27-AEB3-9A7070DEA37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 08-10-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 09-10-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A73DF3-086A-4F27-AEB3-9A7070DEA37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C023387-CEF5-49B9-9FEE-E28A6ECBDA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygesikringssystemer_excel.XLSX
+++ b/html/Sygesikringssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C023387-CEF5-49B9-9FEE-E28A6ECBDA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EA629BBF4865BEBE118B2E0BA6B59FB670D8A5DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1428D906-60DD-4095-823E-7C7FD83FF221}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygesikringssystemer">'Opdateret d. 09-10-2026'!$A$1:$D$21</definedName>
+    <definedName name="Sygesikringssystemer">'Opdateret d. 23-10-2026'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
